--- a/R/advice/advice_basis.xlsx
+++ b/R/advice/advice_basis.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuille1" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="Feuille1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -37,8 +37,8 @@
 HELCOM’s Baltic Sea Action Plan (BSAP) contains several targets for European eel [@helcom2021a].  
 National conservation measures are contained in the report of the Workshop for the Technical evaluation of EU Member States' Progress Reports for submission in 2022 and 2025 [@ices2022c; @ices2025], Eel Management Plan progress reports submitted in 2024, and the country reports of the Joint ICES/European Inland Fisheries and Aquaculture Advisory Commission (EIFAAC)/General Fisheries Commission for the Mediterranean (GFCM) Working Group on Eels [@ices2022a; @ices2024a]. 
 Other international legislations/communications relevant to eel conservation:  
-\- Directive 2000/60/EC, known as the Water Framework Directive (WFD; [@eu2000]) 
-\- Directive 2008/56/EC, known as the Marine Strategy Framework Directive (MSFD; [@eu2008]). 
+\- Directive 2000/60/EC, known as the Water Framework Directive [WFD - @eu2000] 
+\- Directive 2008/56/EC, known as the Marine Strategy Framework Directive [MSFD - @eu2008]. 
 \- Council Directive 92/43/EEC, known as the Habitats Directive [@eu1992] 
 \- The Ramsar Convention on Wetlands [@unitednations1976], which aims to stem the loss of and progressive encroachment on wetlands, an important European eel habitat.  
 \- EU Nature Restoration Law: Regulation (EU) 2024/1991 [@eu2024] 
@@ -118,16 +118,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -143,31 +147,137 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="LibreOffice">
+      <a:dk1>
+        <a:srgbClr val="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="000000"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="FFFFFF"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="18A303"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="0369A3"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A33E03"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="8E03A3"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="C99C00"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="C9211E"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0000EE"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="551A8B"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme>
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="11.66015625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="37.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="80.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="37.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="80.03"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="394.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/R/advice/advice_basis.xlsx
+++ b/R/advice/advice_basis.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
-    <t xml:space="preserve">Advance basis</t>
+    <t xml:space="preserve">Advice basis</t>
   </si>
   <si>
     <t xml:space="preserve">Ecosystem-based management (EBM) considerations</t>
@@ -31,8 +31,8 @@
     <t xml:space="preserve">Existing conservation measures</t>
   </si>
   <si>
-    <t xml:space="preserve">Although the Convention on International Trade in Endangered Species (CITES) is legally binding, it requires specific domestic legislation and measures to allow implementation. For example, European eel (*Anguilla anguilla*) has been listed in the EU implementation of CITES rules (Annex B to Council Regulation [EC] No 338/97; [@eucouncil1996]) since 2009. In 2010, the EU considered that a Non-Detriment Finding could not be developed because of the status of the species, and export and import outside of Member States have not been permitted since that date.  
-A Single Species Action Plan, the mechanism through which coordinated actions are delivered in the Conservation of Migratory Species of Wild Animals (CMS) for European eel, is presently in draft format. 
+    <t xml:space="preserve">Although the CITES is legally binding, it requires specific domestic legislation and measures to allow implementation. For example, European eel has been listed in the EU implementation of CITES rules (Annex B to Council Regulation [EC] No 338/97; [@eucouncil1996]) since 2009. In 2010, the EU considered that a Non-Detriment Finding could not be developed because of the status of the species, and export and import outside of Member States have not been permitted since that date.  
+A Single Species Action Plan, the mechanism through which coordinated actions are delivered in the CMS for European eel, was adopted in March 2026. 
 In 2014, the OSPAR Convention issued a recommendation to strengthen the protection of European eel at all life stages [@ospar2014].  
 HELCOM’s Baltic Sea Action Plan (BSAP) contains several targets for European eel [@helcom2021a].  
 National conservation measures are contained in the report of the Workshop for the Technical evaluation of EU Member States' Progress Reports for submission in 2022 and 2025 [@ices2022c; @ices2025], Eel Management Plan progress reports submitted in 2024, and the country reports of the Joint ICES/European Inland Fisheries and Aquaculture Advisory Commission (EIFAAC)/General Fisheries Commission for the Mediterranean (GFCM) Working Group on Eels [@ices2022a; @ices2024a]. 
